--- a/BD/datos_crudos/bitacora.xlsx
+++ b/BD/datos_crudos/bitacora.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\munos\OneDrive\Desktop\DFBDA_DS321\ProyectoFinal_DFABD_IDS321_Grupo04\datos_crudos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\munos\OneDrive\Desktop\DFBDA_DS321\ProyectoFinal_DFABD_IDS321_Grupo04\BD\datos_crudos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506631B8-B11B-4499-843E-3CEF72ED2D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D31265A-06E8-4FDE-A07B-02AB5C80F406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,40 +19,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="2">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="1"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="2">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-    <bk>
-      <rc t="1" v="1"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="126">
   <si>
     <t>ID</t>
   </si>
@@ -60,10 +28,10 @@
     <t>Fecha</t>
   </si>
   <si>
-    <t>Actividad</t>
-  </si>
-  <si>
-    <t>Decisión técnica</t>
+    <t>Tema</t>
+  </si>
+  <si>
+    <t>Descripción técnica</t>
   </si>
   <si>
     <t>Responsable</t>
@@ -81,194 +49,365 @@
     <t>22/09</t>
   </si>
   <si>
-    <t>Construcción y validación del OLTP OpenFlights</t>
-  </si>
-  <si>
-    <t>Base restaurada desde `.bak` con 5 tablas; limpieza previa: `\N`→NULL, ~530 rutas con aeropuerto inexistente conservan código con FK en NULL, 0 violaciones de FK</t>
-  </si>
-  <si>
-    <t>`openflights_sqlserver.sql` + capturas</t>
-  </si>
-  <si>
-    <t>Completado</t>
+    <t>Error 5 de permisos</t>
+  </si>
+  <si>
+    <t>SSIS no podía leer CSV en `C:\datos_dw`. Solución: permisos NTFS completos a la carpeta</t>
+  </si>
+  <si>
+    <t>Equipo</t>
+  </si>
+  <si>
+    <t>Captura del error</t>
+  </si>
+  <si>
+    <t>Resuelto</t>
   </si>
   <si>
     <t>B-02</t>
   </si>
   <si>
-    <t>Verificación del esquema real del .bak</t>
-  </si>
-  <si>
-    <t>`INFORMATION_SCHEMA` reveló diferencias vs lo supuesto: `airlines.active` es BIT, zona horaria es `tz_olson`, `routes.airline_id` es INT directo, `countries` no tiene continente. Se ajustarán scripts 01/02 a estos nombres</t>
-  </si>
-  <si>
-    <t>Captura INFORMATION_SCHEMA</t>
+    <t>Perfil inicial</t>
+  </si>
+  <si>
+    <t>Conteos y nulos por tabla de staging; cobertura icao_code 12.2%, gps_code 51.6%, iata_code 41.8%</t>
+  </si>
+  <si>
+    <t>Queries de perfil</t>
   </si>
   <si>
     <t>B-03</t>
   </si>
   <si>
-    <t>Descarga de fuentes complementarias</t>
-  </si>
-  <si>
-    <t>OurAirports (airports/regions/countries.csv, dominio público) y OpenSky Zenodo 5815448 (CC-BY). Se eligió **diciembre 2019**: tráfico pre-pandemia y pico estacional visible</t>
-  </si>
-  <si>
-    <t>`fuentes.md` + capturas Zenodo</t>
+    <t>Fuentes documentadas</t>
+  </si>
+  <si>
+    <t>OpenFlights (.bak), OurAirports (3 CSV), OpenSky (1 CSV dic-2019) con roles y URLs en fuentes.md</t>
   </si>
   <si>
     <t>B-04</t>
   </si>
   <si>
-    <t>Carga staging: OS error 5 (Acceso denegado)</t>
-  </si>
-  <si>
-    <t>La cuenta de servicio de SQL Server no tiene lectura sobre carpetas sincronizadas con OneDrive. Se creó copia de trabajo en `C:\datos_dw`; originales permanecen intactos en el repositorio</t>
-  </si>
-  <si>
-    <t>Captura del error + script ajustado</t>
-  </si>
-  <si>
-    <t>Resuelto</t>
+    <t>Modelo estrella</t>
+  </si>
+  <si>
+    <t>Estrella por decisión justificada: jerarquías como atributos, una sola tabla de hechos</t>
+  </si>
+  <si>
+    <t>Diagrama</t>
   </si>
   <si>
     <t>B-05</t>
   </si>
   <si>
-    <t>Falso positivo del editor en BULK INSERT</t>
-  </si>
-  <si>
-    <t>Azure Data Studio marcó `FORMAT='CSV'`/`FIELDQUOTE` como inválidos; se confirmó con `SERVERPROPERTY('ProductMajorVersion')=17` (SQL Server 2025) que el motor sí los soporta (existen desde 2017). El subrayado es cosmético</t>
-  </si>
-  <si>
-    <t>Captura de versión</t>
+    <t>23/09</t>
+  </si>
+  <si>
+    <t>Crosswalk xw_rutas_icao</t>
+  </si>
+  <si>
+    <t>Pre-calcula 36,907 pares ICAO ofertados: EsRutaOfertada como equi-join rápido sobre 2M de filas</t>
+  </si>
+  <si>
+    <t>Script 01</t>
   </si>
   <si>
     <t>B-06</t>
   </si>
   <si>
-    <t>Esquema real de OpenSky difiere del supuesto</t>
-  </si>
-  <si>
-    <t>No trae `icao24`: la llave natural pasa a ser `(aircraft_uid, firstseen)`; `firstseen/lastseen` vienen como datetime con offset (no epoch); `day` = día UTC del último mensaje; coordenadas incluidas. Decisión: staging todo VARCHAR + `TRY_CONVERT` en el ETL</t>
-  </si>
-  <si>
-    <t>Captura de encabezados CSV</t>
+    <t>Aterrizaje crudo</t>
+  </si>
+  <si>
+    <t>Staging todo VARCHAR; tipado y conversión en el ETL con TRY_CONVERT</t>
+  </si>
+  <si>
+    <t>Script 00</t>
   </si>
   <si>
     <t>B-07</t>
   </si>
   <si>
-    <t>OurAirports expone `icao_code` y `gps_code`</t>
-  </si>
-  <si>
-    <t>El archivo trae 19 columnas con ambos códigos; se adopta `icao_code` como canónico para emparejar con OpenSky</t>
-  </si>
-  <si>
-    <t>Captura de encabezado</t>
+    <t>Miembros -1</t>
+  </si>
+  <si>
+    <t>Fila Desconocido por dimensión: la cola larga de OpenSky se mide, no se descarta</t>
   </si>
   <si>
     <t>B-08</t>
   </si>
   <si>
-    <t>Truncamiento de `typecode` (VARCHAR(4))</t>
-  </si>
-  <si>
-    <t>Errores de conversión en filas 54287, 62730, 113906, 125140, 133718...: la fuente trae códigos de hasta 26 caracteres. Se amplió a VARCHAR(30) y se recargó con MAXERRORS=0 sin errores</t>
-  </si>
-  <si>
-    <t>Captura del error + consulta de typecode largos</t>
+    <t>typecode largo</t>
+  </si>
+  <si>
+    <t>VARCHAR(30) tras hallar códigos de hasta 26 caracteres en OpenSky</t>
+  </si>
+  <si>
+    <t>Perfil</t>
   </si>
   <si>
     <t>B-09</t>
   </si>
   <si>
-    <t>Perfil y calidad del staging</t>
-  </si>
-  <si>
-    <t>2,701,295 vuelos (0 sin aircraft_uid; 753,490 sin origin = 27.9%; 714,329 sin typecode = 26.4%). 258,348 aeropuertos (87.8% sin ICAO, **esperado**: solo el servicio programado recibe códigos). 11,961 regiones, 747 países</t>
-  </si>
-  <si>
-    <t>Captura del perfil</t>
+    <t>Simulación gobernable</t>
+  </si>
+  <si>
+    <t>ParametrosSimulacion con 7 constantes; reproducibilidad con CHECKSUM, nunca NEWID()</t>
   </si>
   <si>
     <t>B-10</t>
   </si>
   <si>
-    <t>Vuelos con cruce de frontera UTC</t>
-  </si>
-  <si>
-    <t>Filas con `firstseen` 30-nov pero `day` 01-dic. Decisión: la FechaKey del hecho se toma de `day` (criterio de la fuente), documentado como regla de negocio</t>
-  </si>
-  <si>
-    <t>Fila de ejemplo del CSV</t>
+    <t>Criterio FechaKey</t>
+  </si>
+  <si>
+    <t>Fecha del vuelo = campo day de OpenSky (criterio de la fuente), no firstseen</t>
+  </si>
+  <si>
+    <t>Anexo DimFecha</t>
   </si>
   <si>
     <t>B-11</t>
   </si>
   <si>
-    <t>Definición del esquema dimensional</t>
-  </si>
-  <si>
-    <t>Estrella justificada (galaxia prohibida por cátedra); una sola fact (FactVuelos, grano: 1 vuelo ADS-B); oferta de rutas como bandera degenerada `EsRutaOfertada`; DimAeropuerto con dos roles (origen/destino)</t>
-  </si>
-  <si>
-    <t>Diagrama + párrafo de justificación</t>
+    <t>Idempotencia por patrón</t>
+  </si>
+  <si>
+    <t>Dims por Lookup no-match; hecho por TRUNCATE + carga completa</t>
+  </si>
+  <si>
+    <t>Paquete SSIS</t>
   </si>
   <si>
     <t>B-12</t>
   </si>
   <si>
-    <t>Gobernanza de medidas simuladas</t>
-  </si>
-  <si>
-    <t>Cátedra permite datos ficticios con sentido: no se inventan vuelos; parámetros en `ParametrosSimulacion`; reproducibilidad con `ABS(CHECKSUM(...))` (nunca `NEWID()`); nombres y documentación indican "estimado"</t>
-  </si>
-  <si>
-    <t>Script 00</t>
+    <t>24/09</t>
+  </si>
+  <si>
+    <t>BypassPrepare con DDL</t>
+  </si>
+  <si>
+    <t>OLE DB no prepara TRUNCATE: BypassPrepare=True en tareas con DDL</t>
+  </si>
+  <si>
+    <t>Captura + tarea verde</t>
   </si>
   <si>
     <t>B-13</t>
   </si>
   <si>
-    <t>Índices de apoyo en staging</t>
-  </si>
-  <si>
-    <t>`ix_oa_stg_icao`, `ix_os_stg_origen`, `ix_os_stg_dest` para acelerar la medición de cobertura y los lookups del ETL</t>
-  </si>
-  <si>
-    <t>Script</t>
+    <t>BypassPrepare sin DDL</t>
+  </si>
+  <si>
+    <t>False en tareas sin DDL para validar en diseño con Analizar consulta</t>
+  </si>
+  <si>
+    <t>Documentación</t>
   </si>
   <si>
     <t>B-14</t>
   </si>
   <si>
-    <t>Medición de cobertura OpenSky en OpenFlights vs OurAirports</t>
-  </si>
-  <si>
-    <t>Marvin</t>
+    <t>Fusión icao+gps</t>
+  </si>
+  <si>
+    <t>COALESCE(icao_code, gps_code) como código ICAO único: ninguna columna cubría sola</t>
+  </si>
+  <si>
+    <t>Perfil + DF OA</t>
   </si>
   <si>
     <t>B-15</t>
   </si>
   <si>
-    <t>De 11,407 aeropuertos distintos, 3,310 (29%) están catalogados pero concentran 91.8% de los vuelos (cola larga). Sin OurAirports, 160,696 vuelos (8.2%) caerían en -1; sin OpenFlights, 181,318 (9.3%). Se confirma maestro OurAirports + complemento OpenFlights + hechos OpenSky. Matching del ETL usará COALESCE(icao_code, gps_code)</t>
+    <t>Validación de tareas DDL</t>
+  </si>
+  <si>
+    <t>Por ejecución real y conteo, no por botón Analizar (rechaza SQL válido con DDL)</t>
+  </si>
+  <si>
+    <t>Captura</t>
+  </si>
+  <si>
+    <t>B-16</t>
+  </si>
+  <si>
+    <t>Multi-equipment</t>
+  </si>
+  <si>
+    <t>Cadenas multi-código de routes se conservan como BK de DimAvion; limitación documentada</t>
+  </si>
+  <si>
+    <t>Preview DF_DimAvion</t>
+  </si>
+  <si>
+    <t>B-17</t>
+  </si>
+  <si>
+    <t>Mismatch unicode en Lookup</t>
+  </si>
+  <si>
+    <t>UNION VARCHAR+NVARCHAR promueve a unicode; SSIS no convierte llaves: CAST explícito / Derived Column (DT_STR)</t>
+  </si>
+  <si>
+    <t>Captura + source corregido</t>
+  </si>
+  <si>
+    <t>B-18</t>
+  </si>
+  <si>
+    <t>Git bloqueado por cache VS</t>
+  </si>
+  <si>
+    <t>Permission denied sobre .vs/*.vsidx: .gitignore (.vs/, *.vsidx, bin/, obj/, crudos) + git rm --cached</t>
+  </si>
+  <si>
+    <t>Captura + git ls-files limpio</t>
+  </si>
+  <si>
+    <t>B-19</t>
+  </si>
+  <si>
+    <t>Auditoría de esquema</t>
+  </si>
+  <si>
+    <t>Faltaban RegionCodigo/RegionNombre y había typos Contienente/IACO/Callsing: recreación migrada de DimAeropuerto/DimAerolinea/FactVuelos preservando DimAvion y xw</t>
+  </si>
+  <si>
+    <t>Migración + INFORMATION_SCHEMA</t>
+  </si>
+  <si>
+    <t>B-20</t>
+  </si>
+  <si>
+    <t>Re-ejecución sin migración</t>
+  </si>
+  <si>
+    <t>Guards IF OBJECT_ID protegieron al esquema viejo (errores 1913/207/2627): migración DROP+CREATE y guards en tablas, índices y semillas</t>
+  </si>
+  <si>
+    <t>Log de consola</t>
+  </si>
+  <si>
+    <t>B-21</t>
+  </si>
+  <si>
+    <t>Basura 'N/A' en airlines.icao</t>
+  </si>
+  <si>
+    <t>CASE mixto INT/NVARCHAR en PARTITION BY convertía 'N/A' a int: basura→NULL y partición con clave textual</t>
+  </si>
+  <si>
+    <t>B-22</t>
+  </si>
+  <si>
+    <t>Colisión '?' en índice único</t>
+  </si>
+  <si>
+    <t>Basura unicode casteada a '?' literal violaba UX_DimAerolinea_ICAO: regla de validez ICAO LIKE '[A-Z0-9]'×3/×4 en salida y particionado</t>
+  </si>
+  <si>
+    <t>Log + consulta basura=0</t>
+  </si>
+  <si>
+    <t>B-23</t>
+  </si>
+  <si>
+    <t>NULL en columna IDENTITY</t>
+  </si>
+  <si>
+    <t>Checkboxes de salida del Lookup agregaron columna fantasma auto-mapeada a AeropuertoKey: sin checkboxes, mapeos explícitos, IDENTITY nunca se mapea</t>
+  </si>
+  <si>
+    <t>Log + mapeos limpios</t>
+  </si>
+  <si>
+    <t>B-24</t>
+  </si>
+  <si>
+    <t>Staging triplicado</t>
+  </si>
+  <si>
+    <t>258,348 filas eran 86,116 aeropuertos ×3 por BULK re-ejecutados: dedup post-carga con ROW_NUMBER y regla de reset también en staging</t>
+  </si>
+  <si>
+    <t>Diagnóstico + dedup + conteos</t>
+  </si>
+  <si>
+    <t>B-25</t>
+  </si>
+  <si>
+    <t>25/09</t>
+  </si>
+  <si>
+    <t>Reset sin guarda de -1</t>
+  </si>
+  <si>
+    <t>DELETE pelón eliminaba miembros -1: reset con WHERE Key &lt;&gt; -1; los -1 son datos de diseño, no de carga</t>
+  </si>
+  <si>
+    <t>Log + 1/1/1</t>
+  </si>
+  <si>
+    <t>B-26</t>
+  </si>
+  <si>
+    <t>Semilla -1 fantasma</t>
+  </si>
+  <si>
+    <t>Guarda por subrogada no detectó semilla con BK=-1 y otra subrogada (violación UNIQUE): siembras y limpiezas por llave de negocio</t>
+  </si>
+  <si>
+    <t>Captura + cleanup</t>
+  </si>
+  <si>
+    <t>B-27</t>
+  </si>
+  <si>
+    <t>Fact con joins inactivos</t>
+  </si>
+  <si>
+    <t>Primera corrida dio km/ingresos NULL y EsRutaOfertada todo false: Source del DF_FactVuelos con SQL mutilado (faltaban joins dd y x); re-pegado del SQL canónico</t>
+  </si>
+  <si>
+    <t>Diagnóstico + LogCarga antes/después</t>
+  </si>
+  <si>
+    <t>B-28</t>
+  </si>
+  <si>
+    <t>Reset unificado en orden de dependencia</t>
+  </si>
+  <si>
+    <t>TRUNCATE del hecho al inicio del paquete (antes que dims, por FK): paquete completo re-ejecutable end-to-end verificado con conteos idénticos</t>
+  </si>
+  <si>
+    <t>Captura paquete 9 verdes ×2</t>
+  </si>
+  <si>
+    <t>B-29</t>
+  </si>
+  <si>
+    <t>Verificación cruzada como método</t>
+  </si>
+  <si>
+    <t>Consultas "debería vs cargado" (staging vs fact) adoptadas como chequeo obligatorio post-carga: fue lo que detectó B-24 y B-27</t>
+  </si>
+  <si>
+    <t>Queries de diagnóstico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">README </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -294,9 +433,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -312,75 +450,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>1</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-  <rel r:id="rId2"/>
-</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -705,18 +774,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="10.875" customWidth="1"/>
-    <col min="3" max="3" width="52.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="214.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.875" customWidth="1"/>
+    <col min="4" max="4" width="145.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="6" max="6" width="33.125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -739,7 +808,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -753,62 +822,62 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -822,21 +891,21 @@
         <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>24</v>
       </c>
       <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>26</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
@@ -845,21 +914,21 @@
         <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>29</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
         <v>31</v>
@@ -868,21 +937,21 @@
         <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>33</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
         <v>35</v>
@@ -891,191 +960,525 @@
         <v>36</v>
       </c>
       <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" t="s">
         <v>64</v>
       </c>
-      <c r="F8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" t="s">
         <v>53</v>
       </c>
-      <c r="G12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" t="s">
-        <v>64</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" t="s">
-        <v>64</v>
-      </c>
-      <c r="F14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="C16" t="s">
         <v>66</v>
       </c>
-      <c r="E15" t="s">
-        <v>64</v>
-      </c>
-      <c r="F15" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F16" s="1" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" t="s">
+        <v>95</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>100</v>
+      </c>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" t="s">
+        <v>103</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" t="s">
+        <v>107</v>
+      </c>
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" t="s">
+        <v>108</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" t="s">
+        <v>112</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" t="s">
+        <v>114</v>
+      </c>
+      <c r="D28" t="s">
+        <v>115</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" t="s">
+        <v>116</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B29" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" t="s">
+        <v>118</v>
+      </c>
+      <c r="D29" t="s">
+        <v>119</v>
+      </c>
+      <c r="E29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" t="s">
+        <v>120</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>121</v>
+      </c>
+      <c r="B30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30" t="s">
+        <v>123</v>
+      </c>
+      <c r="E30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" t="s">
+        <v>124</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G1 A15 A2:D11 F2:G13 G14 C15 A12:A14 C12:D14" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G3 A5:G30 A4:E4 G4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>